--- a/src/evaluation/data/Backup/scraping_stats_SemanticChunking.xlsx
+++ b/src/evaluation/data/Backup/scraping_stats_SemanticChunking.xlsx
@@ -7,9 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Übersicht" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chunking-Parameter" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collections" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +499,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24734</v>
+        <v>52631</v>
       </c>
     </row>
     <row r="8">
@@ -511,216 +509,174 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.25</v>
+        <v>19.68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dokumente übersprungen</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
+          <t>Durchschn. Chunk-Größe</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1152.53 Zeichen</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fehler</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
+          <t>Min Chunk-Größe</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>17 Zeichen</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gesamtzeit (Minuten)</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>33.84</v>
+          <t>Max Chunk-Größe</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1500 Zeichen</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gesamtzeit (Sekunden)</t>
+          <t>Dokumente übersprungen</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2030</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dokumente/Sekunde</t>
+          <t>Fehler</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Startzeit</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2025-12-04 09:27:17</t>
-        </is>
+          <t>Gesamtzeit (Minuten)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>40.08</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Gesamtzeit (Sekunden)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Dokumente/Sekunde</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Startzeit</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-12-04 11:34:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Endzeit</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2025-12-04 10:01:07</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Wert</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Chunking-Methode</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Semantic Chunking (Embedding-basiert)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Max Chunk Size</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Min Chunk Size</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Overlap</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Similarity Threshold</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Embedding Model</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>paraphrase-multilingual-MiniLM-L12-v2</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Anzahl Chunks</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Anteil (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>wiso_documents</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>24734</v>
-      </c>
-      <c r="C2" t="n">
-        <v>100</v>
-      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-12-04 12:14:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>max_chunk_size</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1500 Zeichen</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>min_chunk_size</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>400 Zeichen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>overlap</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>300 Zeichen</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>similarity_threshold</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Embedding-Modell: paraphrase-multilingual-MiniLM-L12-v2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
